--- a/data/comments/icr4.xlsx
+++ b/data/comments/icr4.xlsx
@@ -11,6 +11,65 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>n_Units</t>
+  </si>
+  <si>
+    <t>n_Coders</t>
+  </si>
+  <si>
+    <t>n_Categories</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Agreement</t>
+  </si>
+  <si>
+    <t>Holstis_CR</t>
+  </si>
+  <si>
+    <t>Krippendorffs_Alpha</t>
+  </si>
+  <si>
+    <t>Cohens_Kappa</t>
+  </si>
+  <si>
+    <t>Lotus</t>
+  </si>
+  <si>
+    <t>S_Lotus</t>
+  </si>
+  <si>
+    <t>pers_exp</t>
+  </si>
+  <si>
+    <t>nominal</t>
+  </si>
+  <si>
+    <t>emot_exp</t>
+  </si>
+  <si>
+    <t>pol_opin</t>
+  </si>
+  <si>
+    <t>breadth</t>
+  </si>
+  <si>
+    <t>valence</t>
+  </si>
+  <si>
+    <t>contr</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,68 +413,44 @@
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>n_Units</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>n_Coders</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>n_Categories</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Agreement</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Holstis_CR</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Krippendorffs_Alpha</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Cohens_Kappa</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Lotus</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>S_Lotus</t>
-        </is>
+    <row r="1" spans="1:11" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>pers_exp</t>
-        </is>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
       </c>
       <c r="B2">
         <v>150</v>
@@ -426,10 +461,8 @@
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>nominal</t>
-        </is>
+      <c r="E2" t="s">
+        <v>12</v>
       </c>
       <c r="F2">
         <v>0.9866666666666667</v>
@@ -450,11 +483,9 @@
         <v>0.9866666666666667</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>emot_exp</t>
-        </is>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>13</v>
       </c>
       <c r="B3">
         <v>150</v>
@@ -465,35 +496,31 @@
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>nominal</t>
-        </is>
+      <c r="E3" t="s">
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>0.9333333333333333</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="G3">
-        <v>0.9333333333333333</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="H3">
-        <v>0.8273273273273274</v>
+        <v>0.8781084386465552</v>
       </c>
       <c r="I3">
-        <v>0.8271092669432919</v>
+        <v>0.8777648428405123</v>
       </c>
       <c r="J3">
-        <v>0.9666666666666667</v>
+        <v>0.9766666666666667</v>
       </c>
       <c r="K3">
-        <v>0.9333333333333333</v>
+        <v>0.9533333333333334</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>pol_opin</t>
-        </is>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>14</v>
       </c>
       <c r="B4">
         <v>150</v>
@@ -504,35 +531,31 @@
       <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>nominal</t>
-        </is>
+      <c r="E4" t="s">
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>0.9333333333333333</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="G4">
-        <v>0.9333333333333333</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="H4">
-        <v>0.8533163265306123</v>
+        <v>0.8986489758365213</v>
       </c>
       <c r="I4">
-        <v>0.8532863849765259</v>
+        <v>0.8984329657573999</v>
       </c>
       <c r="J4">
-        <v>0.9666666666666667</v>
+        <v>0.9766666666666667</v>
       </c>
       <c r="K4">
-        <v>0.9333333333333333</v>
+        <v>0.9533333333333334</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>breadth</t>
-        </is>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>15</v>
       </c>
       <c r="B5">
         <v>150</v>
@@ -543,35 +566,31 @@
       <c r="D5">
         <v>9</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>nominal</t>
-        </is>
+      <c r="E5" t="s">
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>0.8933333333333333</v>
+        <v>0.92</v>
       </c>
       <c r="G5">
-        <v>0.8933333333333333</v>
+        <v>0.92</v>
       </c>
       <c r="H5">
-        <v>0.863216583273767</v>
+        <v>0.8971919770773639</v>
       </c>
       <c r="I5">
-        <v>0.8628336286220497</v>
+        <v>0.8969308291342191</v>
       </c>
       <c r="J5">
-        <v>0.9466666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="K5">
-        <v>0.9399999999999999</v>
+        <v>0.9550000000000001</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>valence</t>
-        </is>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>16</v>
       </c>
       <c r="B6">
         <v>150</v>
@@ -582,35 +601,31 @@
       <c r="D6">
         <v>4</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>nominal</t>
-        </is>
+      <c r="E6" t="s">
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>0.8533333333333334</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="G6">
-        <v>0.8533333333333334</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="H6">
-        <v>0.795071497554441</v>
+        <v>0.8499560908292561</v>
       </c>
       <c r="I6">
-        <v>0.7950055907566157</v>
+        <v>0.8498498498498498</v>
       </c>
       <c r="J6">
-        <v>0.9266666666666667</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="K6">
-        <v>0.9022222222222223</v>
+        <v>0.9288888888888889</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>contr</t>
-        </is>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>17</v>
       </c>
       <c r="B7">
         <v>150</v>
@@ -621,28 +636,26 @@
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>nominal</t>
-        </is>
+      <c r="E7" t="s">
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>0.92</v>
+        <v>0.9266666666666666</v>
       </c>
       <c r="G7">
-        <v>0.92</v>
+        <v>0.9266666666666666</v>
       </c>
       <c r="H7">
-        <v>0.8167892156862745</v>
+        <v>0.8329693768726829</v>
       </c>
       <c r="I7">
-        <v>0.8162140085766797</v>
+        <v>0.8324192565508838</v>
       </c>
       <c r="J7">
-        <v>0.96</v>
+        <v>0.9633333333333334</v>
       </c>
       <c r="K7">
-        <v>0.92</v>
+        <v>0.9266666666666666</v>
       </c>
     </row>
   </sheetData>
